--- a/output/COA Configuration.xlsx
+++ b/output/COA Configuration.xlsx
@@ -56798,86 +56798,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BY8"/>
+  <dimension ref="A1:BZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26.4" customWidth="1" min="1" max="1"/>
-    <col width="25.2" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="20.4" customWidth="1" min="6" max="6"/>
-    <col width="28.8" customWidth="1" min="7" max="7"/>
-    <col width="34.8" customWidth="1" min="8" max="8"/>
-    <col width="31.2" customWidth="1" min="9" max="9"/>
-    <col width="21.6" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26.4" customWidth="1" min="2" max="2"/>
+    <col width="25.2" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="20.4" customWidth="1" min="7" max="7"/>
+    <col width="28.8" customWidth="1" min="8" max="8"/>
+    <col width="34.8" customWidth="1" min="9" max="9"/>
+    <col width="31.2" customWidth="1" min="10" max="10"/>
     <col width="21.6" customWidth="1" min="11" max="11"/>
-    <col width="25.2" customWidth="1" min="12" max="12"/>
-    <col width="30" customWidth="1" min="13" max="13"/>
-    <col width="26.4" customWidth="1" min="14" max="14"/>
-    <col width="19.2" customWidth="1" min="15" max="15"/>
-    <col width="21.6" customWidth="1" min="16" max="16"/>
-    <col width="34.8" customWidth="1" min="17" max="17"/>
-    <col width="20.4" customWidth="1" min="18" max="18"/>
-    <col width="19.2" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
-    <col width="14.4" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="13.2" customWidth="1" min="23" max="23"/>
-    <col width="38.4" customWidth="1" min="24" max="24"/>
+    <col width="21.6" customWidth="1" min="12" max="12"/>
+    <col width="25.2" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="26.4" customWidth="1" min="15" max="15"/>
+    <col width="19.2" customWidth="1" min="16" max="16"/>
+    <col width="21.6" customWidth="1" min="17" max="17"/>
+    <col width="34.8" customWidth="1" min="18" max="18"/>
+    <col width="20.4" customWidth="1" min="19" max="19"/>
+    <col width="19.2" customWidth="1" min="20" max="20"/>
+    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="14.4" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="13.2" customWidth="1" min="24" max="24"/>
     <col width="38.4" customWidth="1" min="25" max="25"/>
     <col width="38.4" customWidth="1" min="26" max="26"/>
     <col width="38.4" customWidth="1" min="27" max="27"/>
     <col width="38.4" customWidth="1" min="28" max="28"/>
     <col width="38.4" customWidth="1" min="29" max="29"/>
-    <col width="22.8" customWidth="1" min="30" max="30"/>
-    <col width="40.8" customWidth="1" min="31" max="31"/>
+    <col width="38.4" customWidth="1" min="30" max="30"/>
+    <col width="22.8" customWidth="1" min="31" max="31"/>
     <col width="40.8" customWidth="1" min="32" max="32"/>
     <col width="40.8" customWidth="1" min="33" max="33"/>
     <col width="40.8" customWidth="1" min="34" max="34"/>
     <col width="40.8" customWidth="1" min="35" max="35"/>
     <col width="40.8" customWidth="1" min="36" max="36"/>
-    <col width="25.2" customWidth="1" min="37" max="37"/>
-    <col width="20.4" customWidth="1" min="38" max="38"/>
-    <col width="15.6" customWidth="1" min="39" max="39"/>
-    <col width="12" customWidth="1" min="40" max="40"/>
-    <col width="25.2" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="13.2" customWidth="1" min="43" max="43"/>
-    <col width="24" customWidth="1" min="44" max="44"/>
-    <col width="19.2" customWidth="1" min="45" max="45"/>
-    <col width="26.4" customWidth="1" min="46" max="46"/>
+    <col width="40.8" customWidth="1" min="37" max="37"/>
+    <col width="25.2" customWidth="1" min="38" max="38"/>
+    <col width="20.4" customWidth="1" min="39" max="39"/>
+    <col width="15.6" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="41" max="41"/>
+    <col width="25.2" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="13.2" customWidth="1" min="44" max="44"/>
+    <col width="24" customWidth="1" min="45" max="45"/>
+    <col width="19.2" customWidth="1" min="46" max="46"/>
     <col width="26.4" customWidth="1" min="47" max="47"/>
-    <col width="42" customWidth="1" min="48" max="48"/>
-    <col width="8.4" customWidth="1" min="49" max="49"/>
-    <col width="19.2" customWidth="1" min="50" max="50"/>
-    <col width="24" customWidth="1" min="51" max="51"/>
-    <col width="16.8" customWidth="1" min="52" max="52"/>
-    <col width="21.6" customWidth="1" min="53" max="53"/>
-    <col width="22.8" customWidth="1" min="54" max="54"/>
-    <col width="26.4" customWidth="1" min="55" max="55"/>
-    <col width="20.4" customWidth="1" min="56" max="56"/>
-    <col width="21.6" customWidth="1" min="57" max="57"/>
-    <col width="22.8" customWidth="1" min="58" max="58"/>
-    <col width="26.4" customWidth="1" min="59" max="59"/>
-    <col width="39.6" customWidth="1" min="60" max="60"/>
+    <col width="26.4" customWidth="1" min="48" max="48"/>
+    <col width="42" customWidth="1" min="49" max="49"/>
+    <col width="8.4" customWidth="1" min="50" max="50"/>
+    <col width="19.2" customWidth="1" min="51" max="51"/>
+    <col width="24" customWidth="1" min="52" max="52"/>
+    <col width="16.8" customWidth="1" min="53" max="53"/>
+    <col width="21.6" customWidth="1" min="54" max="54"/>
+    <col width="22.8" customWidth="1" min="55" max="55"/>
+    <col width="26.4" customWidth="1" min="56" max="56"/>
+    <col width="20.4" customWidth="1" min="57" max="57"/>
+    <col width="21.6" customWidth="1" min="58" max="58"/>
+    <col width="22.8" customWidth="1" min="59" max="59"/>
+    <col width="26.4" customWidth="1" min="60" max="60"/>
     <col width="39.6" customWidth="1" min="61" max="61"/>
     <col width="39.6" customWidth="1" min="62" max="62"/>
     <col width="39.6" customWidth="1" min="63" max="63"/>
     <col width="39.6" customWidth="1" min="64" max="64"/>
     <col width="39.6" customWidth="1" min="65" max="65"/>
-    <col width="36" customWidth="1" min="66" max="66"/>
-    <col width="31.2" customWidth="1" min="67" max="67"/>
-    <col width="34.8" customWidth="1" min="68" max="68"/>
-    <col width="21.6" customWidth="1" min="69" max="69"/>
-    <col width="28.8" customWidth="1" min="70" max="70"/>
-    <col width="26.4" customWidth="1" min="71" max="71"/>
+    <col width="39.6" customWidth="1" min="66" max="66"/>
+    <col width="36" customWidth="1" min="67" max="67"/>
+    <col width="31.2" customWidth="1" min="68" max="68"/>
+    <col width="34.8" customWidth="1" min="69" max="69"/>
+    <col width="21.6" customWidth="1" min="70" max="70"/>
+    <col width="28.8" customWidth="1" min="71" max="71"/>
     <col width="26.4" customWidth="1" min="72" max="72"/>
-    <col width="32.4" customWidth="1" min="73" max="73"/>
+    <col width="26.4" customWidth="1" min="73" max="73"/>
     <col width="32.4" customWidth="1" min="74" max="74"/>
-    <col width="40.8" customWidth="1" min="75" max="75"/>
+    <col width="32.4" customWidth="1" min="75" max="75"/>
     <col width="40.8" customWidth="1" min="76" max="76"/>
-    <col width="7.199999999999999" customWidth="1" min="77" max="77"/>
+    <col width="40.8" customWidth="1" min="77" max="77"/>
+    <col width="43.2" customWidth="1" min="78" max="78"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -56904,768 +56905,782 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Accounting dimension</t>
+          <t>Division</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Accounting identity</t>
+          <t>Accounting dimension</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>Account group</t>
+          <t>Accounting identity</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Account group</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F5" s="26" t="inlineStr">
         <is>
-          <t>Balance account</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t>Profit or loss account</t>
+          <t>Balance account</t>
         </is>
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>Accounts receivable account</t>
+          <t>Profit or loss account</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t>Accounts payable account</t>
+          <t>Accounts receivable account</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr">
         <is>
-          <t>VAT account type</t>
+          <t>Accounts payable account</t>
         </is>
       </c>
       <c r="K5" s="26" t="inlineStr">
         <is>
-          <t>Internal account</t>
+          <t>VAT account type</t>
         </is>
       </c>
       <c r="L5" s="26" t="inlineStr">
         <is>
-          <t>Revaluation account</t>
+          <t>Internal account</t>
         </is>
       </c>
       <c r="M5" s="26" t="inlineStr">
         <is>
-          <t>Cost of capital account</t>
+          <t>Revaluation account</t>
         </is>
       </c>
       <c r="N5" s="26" t="inlineStr">
         <is>
-          <t>Fixed assets account</t>
+          <t>Cost of capital account</t>
         </is>
       </c>
       <c r="O5" s="26" t="inlineStr">
         <is>
-          <t>Period account</t>
+          <t>Fixed assets account</t>
         </is>
       </c>
       <c r="P5" s="26" t="inlineStr">
         <is>
-          <t>Clearing account</t>
+          <t>Period account</t>
         </is>
       </c>
       <c r="Q5" s="26" t="inlineStr">
         <is>
-          <t>Blocked accounting identity</t>
+          <t>Clearing account</t>
         </is>
       </c>
       <c r="R5" s="26" t="inlineStr">
         <is>
-          <t>Outcome account</t>
+          <t>Blocked accounting identity</t>
         </is>
       </c>
       <c r="S5" s="26" t="inlineStr">
         <is>
-          <t>Budget account</t>
+          <t>Outcome account</t>
         </is>
       </c>
       <c r="T5" s="26" t="inlineStr">
         <is>
-          <t>Cost accounting account</t>
+          <t>Budget account</t>
         </is>
       </c>
       <c r="U5" s="26" t="inlineStr">
         <is>
-          <t>Valid from</t>
+          <t>Cost accounting account</t>
         </is>
       </c>
       <c r="V5" s="26" t="inlineStr">
         <is>
-          <t>Valid to</t>
+          <t>Valid from</t>
         </is>
       </c>
       <c r="W5" s="26" t="inlineStr">
         <is>
-          <t>Archiving</t>
+          <t>Valid to</t>
         </is>
       </c>
       <c r="X5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 2</t>
+          <t>Archiving</t>
         </is>
       </c>
       <c r="Y5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 3</t>
+          <t>ACR for accounting dimension 2</t>
         </is>
       </c>
       <c r="Z5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 4</t>
+          <t>ACR for accounting dimension 3</t>
         </is>
       </c>
       <c r="AA5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 5</t>
+          <t>ACR for accounting dimension 4</t>
         </is>
       </c>
       <c r="AB5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 6</t>
+          <t>ACR for accounting dimension 5</t>
         </is>
       </c>
       <c r="AC5" s="26" t="inlineStr">
         <is>
-          <t>ACR for accounting dimension 7</t>
+          <t>ACR for accounting dimension 6</t>
         </is>
       </c>
       <c r="AD5" s="26" t="inlineStr">
         <is>
-          <t>ACR for VAT codes</t>
+          <t>ACR for accounting dimension 7</t>
         </is>
       </c>
       <c r="AE5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 2 (budget)</t>
+          <t>ACR for VAT codes</t>
         </is>
       </c>
       <c r="AF5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 3 (budget)</t>
+          <t>ACR for acc dimension 2 (budget)</t>
         </is>
       </c>
       <c r="AG5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 4 (budget)</t>
+          <t>ACR for acc dimension 3 (budget)</t>
         </is>
       </c>
       <c r="AH5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 5 (budget)</t>
+          <t>ACR for acc dimension 4 (budget)</t>
         </is>
       </c>
       <c r="AI5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 6 (budget)</t>
+          <t>ACR for acc dimension 5 (budget)</t>
         </is>
       </c>
       <c r="AJ5" s="26" t="inlineStr">
         <is>
-          <t>ACR for acc dimension 7 (budget)</t>
+          <t>ACR for acc dimension 6 (budget)</t>
         </is>
       </c>
       <c r="AK5" s="26" t="inlineStr">
         <is>
-          <t>Object access group</t>
+          <t>ACR for acc dimension 7 (budget)</t>
         </is>
       </c>
       <c r="AL5" s="26" t="inlineStr">
         <is>
-          <t>Authority group</t>
+          <t>Object access group</t>
         </is>
       </c>
       <c r="AM5" s="26" t="inlineStr">
         <is>
-          <t>Responsible</t>
+          <t>Authority group</t>
         </is>
       </c>
       <c r="AN5" s="26" t="inlineStr">
         <is>
-          <t>VAT code</t>
+          <t>Responsible</t>
         </is>
       </c>
       <c r="AO5" s="26" t="inlineStr">
         <is>
-          <t>Currency connection</t>
+          <t>VAT code</t>
         </is>
       </c>
       <c r="AP5" s="26" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Currency connection</t>
         </is>
       </c>
       <c r="AQ5" s="26" t="inlineStr">
         <is>
-          <t>Sign lock</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="AR5" s="26" t="inlineStr">
         <is>
-          <t>Quantity mandatory</t>
+          <t>Sign lock</t>
         </is>
       </c>
       <c r="AS5" s="26" t="inlineStr">
         <is>
-          <t>Text mandatory</t>
+          <t>Quantity mandatory</t>
         </is>
       </c>
       <c r="AT5" s="26" t="inlineStr">
         <is>
-          <t>Replacement category</t>
+          <t>Text mandatory</t>
         </is>
       </c>
       <c r="AU5" s="26" t="inlineStr">
         <is>
-          <t>Cost of capital rule</t>
+          <t>Replacement category</t>
         </is>
       </c>
       <c r="AV5" s="26" t="inlineStr">
         <is>
-          <t>Transaction check before deletion</t>
+          <t>Cost of capital rule</t>
         </is>
       </c>
       <c r="AW5" s="26" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Transaction check before deletion</t>
         </is>
       </c>
       <c r="AX5" s="26" t="inlineStr">
         <is>
-          <t>Reconciliation</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="AY5" s="26" t="inlineStr">
         <is>
-          <t>Petty cash account</t>
+          <t>Reconciliation</t>
         </is>
       </c>
       <c r="AZ5" s="26" t="inlineStr">
         <is>
-          <t>Bank account</t>
+          <t>Petty cash account</t>
         </is>
       </c>
       <c r="BA5" s="26" t="inlineStr">
         <is>
-          <t>Suspense account</t>
+          <t>Bank account</t>
         </is>
       </c>
       <c r="BB5" s="26" t="inlineStr">
         <is>
-          <t>Inventory account</t>
+          <t>Suspense account</t>
         </is>
       </c>
       <c r="BC5" s="26" t="inlineStr">
         <is>
-          <t>Enter bank operation</t>
+          <t>Inventory account</t>
         </is>
       </c>
       <c r="BD5" s="26" t="inlineStr">
         <is>
-          <t>Resource driver</t>
+          <t>Enter bank operation</t>
         </is>
       </c>
       <c r="BE5" s="26" t="inlineStr">
         <is>
-          <t>Variable percent</t>
+          <t>Resource driver</t>
         </is>
       </c>
       <c r="BF5" s="26" t="inlineStr">
         <is>
-          <t>Cost center model</t>
+          <t>Variable percent</t>
         </is>
       </c>
       <c r="BG5" s="26" t="inlineStr">
         <is>
-          <t>Consolidation method</t>
+          <t>Cost center model</t>
         </is>
       </c>
       <c r="BH5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 2</t>
+          <t>Consolidation method</t>
         </is>
       </c>
       <c r="BI5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 3</t>
+          <t>Compress accounting dimension 2</t>
         </is>
       </c>
       <c r="BJ5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 4</t>
+          <t>Compress accounting dimension 3</t>
         </is>
       </c>
       <c r="BK5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 5</t>
+          <t>Compress accounting dimension 4</t>
         </is>
       </c>
       <c r="BL5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 6</t>
+          <t>Compress accounting dimension 5</t>
         </is>
       </c>
       <c r="BM5" s="26" t="inlineStr">
         <is>
-          <t>Compress accounting dimension 7</t>
+          <t>Compress accounting dimension 6</t>
         </is>
       </c>
       <c r="BN5" s="26" t="inlineStr">
         <is>
-          <t>Delegation of authority code</t>
+          <t>Compress accounting dimension 7</t>
         </is>
       </c>
       <c r="BO5" s="26" t="inlineStr">
         <is>
-          <t>Blocked for manual entry</t>
+          <t>Delegation of authority code</t>
         </is>
       </c>
       <c r="BP5" s="26" t="inlineStr">
         <is>
-          <t>Financial agreement account</t>
+          <t>Blocked for manual entry</t>
         </is>
       </c>
       <c r="BQ5" s="26" t="inlineStr">
         <is>
-          <t>Obsolete account</t>
+          <t>Financial agreement account</t>
         </is>
       </c>
       <c r="BR5" s="26" t="inlineStr">
         <is>
-          <t>Debit/credit code lock</t>
+          <t>Obsolete account</t>
         </is>
       </c>
       <c r="BS5" s="26" t="inlineStr">
         <is>
-          <t>Analysis dimension 1</t>
+          <t>Debit/credit code lock</t>
         </is>
       </c>
       <c r="BT5" s="26" t="inlineStr">
         <is>
-          <t>Analysis dimension 2</t>
+          <t>Analysis dimension 1</t>
         </is>
       </c>
       <c r="BU5" s="26" t="inlineStr">
         <is>
-          <t>Analysis dimension type 1</t>
+          <t>Analysis dimension 2</t>
         </is>
       </c>
       <c r="BV5" s="26" t="inlineStr">
         <is>
-          <t>Analysis dimension type 2</t>
+          <t>Analysis dimension type 1</t>
         </is>
       </c>
       <c r="BW5" s="26" t="inlineStr">
         <is>
-          <t>Analysis dimension description 1</t>
+          <t>Analysis dimension type 2</t>
         </is>
       </c>
       <c r="BX5" s="26" t="inlineStr">
         <is>
+          <t>Analysis dimension description 1</t>
+        </is>
+      </c>
+      <c r="BY5" s="26" t="inlineStr">
+        <is>
           <t>Analysis dimension description 2</t>
         </is>
       </c>
-      <c r="BY5" s="26" t="inlineStr"/>
+      <c r="BZ5" s="26" t="inlineStr">
+        <is>
+          <t>Exclude from  withholding tax base</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>AITP</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>AITM</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>AICL</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>AT01</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>AT02</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>AT03</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>AT11</t>
         </is>
       </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>AT04</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>AT05</t>
         </is>
       </c>
-      <c r="L6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>AT06</t>
         </is>
       </c>
-      <c r="M6" s="27" t="inlineStr">
+      <c r="N6" s="27" t="inlineStr">
         <is>
           <t>AT07</t>
         </is>
       </c>
-      <c r="N6" s="27" t="inlineStr">
+      <c r="O6" s="27" t="inlineStr">
         <is>
           <t>AT08</t>
         </is>
       </c>
-      <c r="O6" s="27" t="inlineStr">
+      <c r="P6" s="27" t="inlineStr">
         <is>
           <t>AT09</t>
         </is>
       </c>
-      <c r="P6" s="27" t="inlineStr">
+      <c r="Q6" s="27" t="inlineStr">
         <is>
           <t>AT10</t>
         </is>
       </c>
-      <c r="Q6" s="27" t="inlineStr">
+      <c r="R6" s="27" t="inlineStr">
         <is>
           <t>LCCD</t>
         </is>
       </c>
-      <c r="R6" s="27" t="inlineStr">
+      <c r="S6" s="27" t="inlineStr">
         <is>
           <t>OUAC</t>
         </is>
       </c>
-      <c r="S6" s="27" t="inlineStr">
+      <c r="T6" s="27" t="inlineStr">
         <is>
           <t>BUAC</t>
         </is>
       </c>
-      <c r="T6" s="27" t="inlineStr">
+      <c r="U6" s="27" t="inlineStr">
         <is>
           <t>CAAC</t>
         </is>
       </c>
-      <c r="U6" s="27" t="inlineStr">
+      <c r="V6" s="27" t="inlineStr">
         <is>
           <t>VFDT</t>
         </is>
       </c>
-      <c r="V6" s="27" t="inlineStr">
+      <c r="W6" s="27" t="inlineStr">
         <is>
           <t>VTDT</t>
         </is>
       </c>
-      <c r="W6" s="27" t="inlineStr">
+      <c r="X6" s="27" t="inlineStr">
         <is>
           <t>ARCH</t>
         </is>
       </c>
-      <c r="X6" s="27" t="inlineStr">
+      <c r="Y6" s="27" t="inlineStr">
         <is>
           <t>ACR2</t>
         </is>
       </c>
-      <c r="Y6" s="27" t="inlineStr">
+      <c r="Z6" s="27" t="inlineStr">
         <is>
           <t>ACR3</t>
         </is>
       </c>
-      <c r="Z6" s="27" t="inlineStr">
+      <c r="AA6" s="27" t="inlineStr">
         <is>
           <t>ACR4</t>
         </is>
       </c>
-      <c r="AA6" s="27" t="inlineStr">
+      <c r="AB6" s="27" t="inlineStr">
         <is>
           <t>ACR5</t>
         </is>
       </c>
-      <c r="AB6" s="27" t="inlineStr">
+      <c r="AC6" s="27" t="inlineStr">
         <is>
           <t>ACR6</t>
         </is>
       </c>
-      <c r="AC6" s="27" t="inlineStr">
+      <c r="AD6" s="27" t="inlineStr">
         <is>
           <t>ACR7</t>
         </is>
       </c>
-      <c r="AD6" s="27" t="inlineStr">
+      <c r="AE6" s="27" t="inlineStr">
         <is>
           <t>ACRV</t>
         </is>
       </c>
-      <c r="AE6" s="27" t="inlineStr">
+      <c r="AF6" s="27" t="inlineStr">
         <is>
           <t>ACB2</t>
         </is>
       </c>
-      <c r="AF6" s="27" t="inlineStr">
+      <c r="AG6" s="27" t="inlineStr">
         <is>
           <t>ACB3</t>
         </is>
       </c>
-      <c r="AG6" s="27" t="inlineStr">
+      <c r="AH6" s="27" t="inlineStr">
         <is>
           <t>ACB4</t>
         </is>
       </c>
-      <c r="AH6" s="27" t="inlineStr">
+      <c r="AI6" s="27" t="inlineStr">
         <is>
           <t>ACB5</t>
         </is>
       </c>
-      <c r="AI6" s="27" t="inlineStr">
+      <c r="AJ6" s="27" t="inlineStr">
         <is>
           <t>ACB6</t>
         </is>
       </c>
-      <c r="AJ6" s="27" t="inlineStr">
+      <c r="AK6" s="27" t="inlineStr">
         <is>
           <t>ACB7</t>
         </is>
       </c>
-      <c r="AK6" s="27" t="inlineStr">
+      <c r="AL6" s="27" t="inlineStr">
         <is>
           <t>ACGR</t>
         </is>
       </c>
-      <c r="AL6" s="27" t="inlineStr">
+      <c r="AM6" s="27" t="inlineStr">
         <is>
           <t>APCG</t>
         </is>
       </c>
-      <c r="AM6" s="27" t="inlineStr">
+      <c r="AN6" s="27" t="inlineStr">
         <is>
           <t>RESP</t>
         </is>
       </c>
-      <c r="AN6" s="27" t="inlineStr">
+      <c r="AO6" s="27" t="inlineStr">
         <is>
           <t>VTCD</t>
         </is>
       </c>
-      <c r="AO6" s="27" t="inlineStr">
+      <c r="AP6" s="27" t="inlineStr">
         <is>
           <t>CCCD</t>
         </is>
       </c>
-      <c r="AP6" s="27" t="inlineStr">
+      <c r="AQ6" s="27" t="inlineStr">
         <is>
           <t>CUCD</t>
         </is>
       </c>
-      <c r="AQ6" s="27" t="inlineStr">
+      <c r="AR6" s="27" t="inlineStr">
         <is>
           <t>SLCD</t>
         </is>
       </c>
-      <c r="AR6" s="27" t="inlineStr">
+      <c r="AS6" s="27" t="inlineStr">
         <is>
           <t>MQCD</t>
         </is>
       </c>
-      <c r="AS6" s="27" t="inlineStr">
+      <c r="AT6" s="27" t="inlineStr">
         <is>
           <t>MTCD</t>
         </is>
       </c>
-      <c r="AT6" s="27" t="inlineStr">
+      <c r="AU6" s="27" t="inlineStr">
         <is>
           <t>SUCT</t>
         </is>
       </c>
-      <c r="AU6" s="27" t="inlineStr">
+      <c r="AV6" s="27" t="inlineStr">
         <is>
           <t>CICT</t>
         </is>
       </c>
-      <c r="AV6" s="27" t="inlineStr">
+      <c r="AW6" s="27" t="inlineStr">
         <is>
           <t>ETCH</t>
         </is>
       </c>
-      <c r="AW6" s="27" t="inlineStr">
+      <c r="AX6" s="27" t="inlineStr">
         <is>
           <t>OBJE</t>
         </is>
       </c>
-      <c r="AX6" s="27" t="inlineStr">
+      <c r="AY6" s="27" t="inlineStr">
         <is>
           <t>RECE</t>
         </is>
       </c>
-      <c r="AY6" s="27" t="inlineStr">
+      <c r="AZ6" s="27" t="inlineStr">
         <is>
           <t>PCA1</t>
         </is>
       </c>
-      <c r="AZ6" s="27" t="inlineStr">
+      <c r="BA6" s="27" t="inlineStr">
         <is>
           <t>AT12</t>
         </is>
       </c>
-      <c r="BA6" s="27" t="inlineStr">
+      <c r="BB6" s="27" t="inlineStr">
         <is>
           <t>CLRA</t>
         </is>
       </c>
-      <c r="BB6" s="27" t="inlineStr">
+      <c r="BC6" s="27" t="inlineStr">
         <is>
           <t>STOA</t>
         </is>
       </c>
-      <c r="BC6" s="27" t="inlineStr">
+      <c r="BD6" s="27" t="inlineStr">
         <is>
           <t>BACR</t>
         </is>
       </c>
-      <c r="BD6" s="27" t="inlineStr">
+      <c r="BE6" s="27" t="inlineStr">
         <is>
           <t>RDRI</t>
         </is>
       </c>
-      <c r="BE6" s="27" t="inlineStr">
+      <c r="BF6" s="27" t="inlineStr">
         <is>
           <t>RDVP</t>
         </is>
       </c>
-      <c r="BF6" s="27" t="inlineStr">
+      <c r="BG6" s="27" t="inlineStr">
         <is>
           <t>CMID</t>
         </is>
       </c>
-      <c r="BG6" s="27" t="inlineStr">
+      <c r="BH6" s="27" t="inlineStr">
         <is>
           <t>GCMT</t>
         </is>
       </c>
-      <c r="BH6" s="27" t="inlineStr">
+      <c r="BI6" s="27" t="inlineStr">
         <is>
           <t>CAD2</t>
         </is>
       </c>
-      <c r="BI6" s="27" t="inlineStr">
+      <c r="BJ6" s="27" t="inlineStr">
         <is>
           <t>CAD3</t>
         </is>
       </c>
-      <c r="BJ6" s="27" t="inlineStr">
+      <c r="BK6" s="27" t="inlineStr">
         <is>
           <t>CAD4</t>
         </is>
       </c>
-      <c r="BK6" s="27" t="inlineStr">
+      <c r="BL6" s="27" t="inlineStr">
         <is>
           <t>CAD5</t>
         </is>
       </c>
-      <c r="BL6" s="27" t="inlineStr">
+      <c r="BM6" s="27" t="inlineStr">
         <is>
           <t>CAD6</t>
         </is>
       </c>
-      <c r="BM6" s="27" t="inlineStr">
+      <c r="BN6" s="27" t="inlineStr">
         <is>
           <t>CAD7</t>
         </is>
       </c>
-      <c r="BN6" s="27" t="inlineStr">
+      <c r="BO6" s="27" t="inlineStr">
         <is>
           <t>DAUC</t>
         </is>
       </c>
-      <c r="BO6" s="27" t="inlineStr">
+      <c r="BP6" s="27" t="inlineStr">
         <is>
           <t>AT13</t>
         </is>
       </c>
-      <c r="BP6" s="27" t="inlineStr">
+      <c r="BQ6" s="27" t="inlineStr">
         <is>
           <t>AT14</t>
         </is>
       </c>
-      <c r="BQ6" s="27" t="inlineStr">
+      <c r="BR6" s="27" t="inlineStr">
         <is>
           <t>OBCC</t>
         </is>
       </c>
-      <c r="BR6" s="27" t="inlineStr">
+      <c r="BS6" s="27" t="inlineStr">
         <is>
           <t>DBCL</t>
         </is>
       </c>
-      <c r="BS6" s="27" t="inlineStr">
+      <c r="BT6" s="27" t="inlineStr">
         <is>
           <t>ADM1</t>
         </is>
       </c>
-      <c r="BT6" s="27" t="inlineStr">
+      <c r="BU6" s="27" t="inlineStr">
         <is>
           <t>ADM2</t>
         </is>
       </c>
-      <c r="BU6" s="27" t="inlineStr">
+      <c r="BV6" s="27" t="inlineStr">
         <is>
           <t>ATP1</t>
         </is>
       </c>
-      <c r="BV6" s="27" t="inlineStr">
+      <c r="BW6" s="27" t="inlineStr">
         <is>
           <t>ATP2</t>
         </is>
       </c>
-      <c r="BW6" s="27" t="inlineStr">
+      <c r="BX6" s="27" t="inlineStr">
         <is>
           <t>AND1</t>
         </is>
       </c>
-      <c r="BX6" s="27" t="inlineStr">
+      <c r="BY6" s="27" t="inlineStr">
         <is>
           <t>AND2</t>
         </is>
       </c>
-      <c r="BY6" s="27" t="inlineStr">
+      <c r="BZ6" s="27" t="inlineStr">
         <is>
           <t>WHBE</t>
         </is>
@@ -57674,12 +57689,12 @@
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
@@ -57699,7 +57714,7 @@
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G7" s="28" t="inlineStr">
@@ -57824,7 +57839,7 @@
       </c>
       <c r="AE7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AF7" s="28" t="inlineStr">
@@ -57869,7 +57884,7 @@
       </c>
       <c r="AN7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AO7" s="28" t="inlineStr">
@@ -57879,12 +57894,12 @@
       </c>
       <c r="AP7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AQ7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AR7" s="28" t="inlineStr">
@@ -57899,7 +57914,7 @@
       </c>
       <c r="AT7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AU7" s="28" t="inlineStr">
@@ -57909,17 +57924,17 @@
       </c>
       <c r="AV7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AW7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AX7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AY7" s="28" t="inlineStr">
@@ -57944,7 +57959,7 @@
       </c>
       <c r="BC7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="BD7" s="28" t="inlineStr">
@@ -57954,17 +57969,17 @@
       </c>
       <c r="BE7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BF7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="BG7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BH7" s="28" t="inlineStr">
@@ -57999,12 +58014,12 @@
       </c>
       <c r="BN7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="BO7" s="28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BP7" s="28" t="inlineStr">
@@ -58034,7 +58049,7 @@
       </c>
       <c r="BU7" s="28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="BV7" s="28" t="inlineStr">
@@ -58054,39 +58069,44 @@
       </c>
       <c r="BY7" s="28" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BZ7" s="28" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="E8" s="29" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
+      <c r="F8" s="29" t="inlineStr">
         <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
@@ -58161,7 +58181,7 @@
       </c>
       <c r="U8" s="29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V8" s="29" t="inlineStr">
@@ -58171,7 +58191,7 @@
       </c>
       <c r="W8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X8" s="29" t="inlineStr">
@@ -58241,7 +58261,7 @@
       </c>
       <c r="AK8" s="29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL8" s="29" t="inlineStr">
@@ -58256,22 +58276,22 @@
       </c>
       <c r="AN8" s="29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AO8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AP8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AR8" s="29" t="inlineStr">
@@ -58286,7 +58306,7 @@
       </c>
       <c r="AT8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AU8" s="29" t="inlineStr">
@@ -58296,17 +58316,17 @@
       </c>
       <c r="AV8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AW8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AX8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AY8" s="29" t="inlineStr">
@@ -58336,22 +58356,22 @@
       </c>
       <c r="BD8" s="29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BE8" s="29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BF8" s="29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BG8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BH8" s="29" t="inlineStr">
@@ -58386,12 +58406,12 @@
       </c>
       <c r="BN8" s="29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BO8" s="29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BP8" s="29" t="inlineStr">
@@ -58421,12 +58441,12 @@
       </c>
       <c r="BU8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BV8" s="29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BW8" s="29" t="inlineStr">
@@ -58436,10 +58456,15 @@
       </c>
       <c r="BX8" s="29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="BY8" s="29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="BZ8" s="29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -58459,21 +58484,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="27.6" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="14.4" customWidth="1" min="8" max="8"/>
-    <col width="27.6" customWidth="1" min="9" max="9"/>
-    <col width="27.6" customWidth="1" min="10" max="10"/>
-    <col width="27.6" customWidth="1" min="11" max="11"/>
-    <col width="27.6" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
+    <col width="26.4" customWidth="1" min="9" max="9"/>
+    <col width="26.4" customWidth="1" min="10" max="10"/>
+    <col width="26.4" customWidth="1" min="11" max="11"/>
+    <col width="26.4" customWidth="1" min="12" max="12"/>
+    <col width="26.4" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -58500,344 +58526,134 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Constant value</t>
+          <t>Division</t>
         </is>
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>Key value</t>
+          <t>Constant value</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Key value</t>
         </is>
       </c>
       <c r="D5" s="26" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F5" s="26" t="inlineStr">
         <is>
-          <t>Sequence within level</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="G5" s="26" t="inlineStr">
         <is>
-          <t>Account group type</t>
+          <t>Reference field LVLS</t>
         </is>
       </c>
       <c r="H5" s="26" t="inlineStr">
         <is>
-          <t>Page break</t>
+          <t>Reference field ACLT</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
         <is>
-          <t>Account group level 1</t>
+          <t>Reference field QRYB</t>
         </is>
       </c>
       <c r="J5" s="26" t="inlineStr">
         <is>
-          <t>Account group level 2</t>
+          <t>Reference field AIC1</t>
         </is>
       </c>
       <c r="K5" s="26" t="inlineStr">
         <is>
-          <t>Account group level 3</t>
+          <t>Reference field AIC2</t>
         </is>
       </c>
       <c r="L5" s="26" t="inlineStr">
         <is>
-          <t>Account group level 4</t>
+          <t>Reference field AIC3</t>
         </is>
       </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t>Reference field AIC4</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="27" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>LVLS</t>
         </is>
       </c>
-      <c r="G6" s="27" t="inlineStr">
+      <c r="H6" s="27" t="inlineStr">
         <is>
           <t>ACLT</t>
         </is>
       </c>
-      <c r="H6" s="27" t="inlineStr">
+      <c r="I6" s="27" t="inlineStr">
         <is>
           <t>QRYB</t>
         </is>
       </c>
-      <c r="I6" s="27" t="inlineStr">
+      <c r="J6" s="27" t="inlineStr">
         <is>
           <t>AIC1</t>
         </is>
       </c>
-      <c r="J6" s="27" t="inlineStr">
+      <c r="K6" s="27" t="inlineStr">
         <is>
           <t>AIC2</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="L6" s="27" t="inlineStr">
         <is>
           <t>AIC3</t>
         </is>
       </c>
-      <c r="L6" s="27" t="inlineStr">
+      <c r="M6" s="27" t="inlineStr">
         <is>
           <t>AIC4</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="D7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F7" s="28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H7" s="28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L7" s="28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" s="29" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="L8" s="29" t="n">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="23" t="inlineStr">
-        <is>
-          <t>← Back to COA Config</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>CRS102: SALES DEPARTMENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25" t="inlineStr">
-        <is>
-          <t>CSYTAB_SDEP: System tables file</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="26" t="inlineStr">
-        <is>
-          <t>Constant value</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>Key value</t>
-        </is>
-      </c>
-      <c r="C5" s="26" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="D5" s="26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="E5" s="26" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="F5" s="26" t="inlineStr">
-        <is>
-          <t>Reference fld PARM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>STCO</t>
-        </is>
-      </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>STKY</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>LNCD</t>
-        </is>
-      </c>
-      <c r="D6" s="27" t="inlineStr">
-        <is>
-          <t>TX40</t>
-        </is>
-      </c>
-      <c r="E6" s="27" t="inlineStr">
-        <is>
-          <t>TX15</t>
-        </is>
-      </c>
-      <c r="F6" s="27" t="inlineStr">
-        <is>
-          <t>PARM</t>
         </is>
       </c>
     </row>
@@ -58872,11 +58688,46 @@
           <t>A</t>
         </is>
       </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H7" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
@@ -58886,20 +58737,236 @@
       </c>
       <c r="C8" s="29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D8" s="29" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="G8" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K8" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" s="29" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>← Back to COA Config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>CRS102: SALES DEPARTMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>CSYTAB_SDEP: System tables file</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>Constant value</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Key value</t>
+        </is>
+      </c>
+      <c r="D5" s="26" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F5" s="26" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t>Reference field PARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>STCO</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>STKY</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>LNCD</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>TX40</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr">
+        <is>
+          <t>TX15</t>
+        </is>
+      </c>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>PARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G8" s="29" t="n">
         <v>200</v>
       </c>
     </row>
